--- a/src/test/resources/testData/excelTestData.xlsx
+++ b/src/test/resources/testData/excelTestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/19dcebdf543d4f4e/Desktop/TestNG/PageObjectModel/src/test/resources/testData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="67" documentId="11_F25DC773A252ABDACC1048D5C1DD6D665ADE58EC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EC469C3C-9501-4B16-9C7A-061E4647B559}"/>
+  <xr:revisionPtr revIDLastSave="70" documentId="11_F25DC773A252ABDACC1048D5C1DD6D665ADE58EC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D70DCAE-DE86-4D08-8398-90F09E6CD9AD}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="doUserReg" sheetId="4" r:id="rId4"/>
     <sheet name="addCustomerTest" sheetId="5" r:id="rId5"/>
     <sheet name="findNewCarTest" sheetId="6" r:id="rId6"/>
+    <sheet name="findCarModelsAndPrices" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="39">
   <si>
     <t>testuser1</t>
   </si>
@@ -807,4 +808,80 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{352802FA-C765-435D-8177-E8E6630D2DCD}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>